--- a/Result/profitability/8342.xlsx
+++ b/Result/profitability/8342.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4625</v>
+        <v>1.61</v>
       </c>
       <c r="N2" t="n">
-        <v>24.32625</v>
+        <v>24.86125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.24375</v>
+        <v>1.26375</v>
       </c>
       <c r="N3" t="n">
-        <v>22.63875</v>
+        <v>23.0975</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04125</v>
+        <v>1.1525</v>
       </c>
       <c r="N4" t="n">
-        <v>22.0225</v>
+        <v>22.23625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9187500000000001</v>
+        <v>1.13625</v>
       </c>
       <c r="N5" t="n">
-        <v>21.0075</v>
+        <v>21.25125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9087499999999999</v>
+        <v>1.01125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.67375</v>
+        <v>20.38375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7074999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="N7" t="n">
-        <v>18.575</v>
+        <v>19.21125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7794,6 +7794,133 @@
       </c>
       <c r="AM58" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>8342</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>443</v>
+      </c>
+      <c r="D59" t="n">
+        <v>315</v>
+      </c>
+      <c r="E59" t="n">
+        <v>128</v>
+      </c>
+      <c r="F59" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="G59" t="n">
+        <v>72</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>16.24%</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>21</v>
+      </c>
+      <c r="J59" t="n">
+        <v>93</v>
+      </c>
+      <c r="K59" t="n">
+        <v>83</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.69375</v>
+      </c>
+      <c r="N59" t="n">
+        <v>25.78875</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0.7172413793103449</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.990000000000002</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.1151328455910667</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.949999999999999</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.07219548315438717</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
